--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -1502,7 +1502,7 @@
         <v>113085365</v>
       </c>
       <c r="B9" t="n">
-        <v>96480</v>
+        <v>96496</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>113158470</v>
       </c>
       <c r="B10" t="n">
-        <v>96264</v>
+        <v>96280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -1502,7 +1502,7 @@
         <v>113085365</v>
       </c>
       <c r="B9" t="n">
-        <v>96496</v>
+        <v>96508</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>113158470</v>
       </c>
       <c r="B10" t="n">
-        <v>96280</v>
+        <v>96292</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -1626,7 +1626,7 @@
         <v>113158470</v>
       </c>
       <c r="B10" t="n">
-        <v>96292</v>
+        <v>96314</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -1626,7 +1626,7 @@
         <v>113158470</v>
       </c>
       <c r="B10" t="n">
-        <v>96314</v>
+        <v>96318</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,136 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113158980</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96313</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogsvägen 350 m S Stora Bjurevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>323299</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6435949</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-11-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-11-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I diket O om skogsvägen. Ett exemplar med två skott av den numera urskilda äkta lopplummern (Huperzia europaea) (Björk 2020). En meter N om denna planta fanns ett mattlummerbestånd med några skaftade sporax.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Uno Unger</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Uno Unger, Stig Ingvarsson, Erik Ljungstrand, Eva Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>113158980</v>
       </c>
       <c r="B11" t="n">
-        <v>96313</v>
+        <v>96320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1877,6 +1877,130 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113633043</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96322</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartsjön, 600 m V om, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>323298</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6435947</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Spekeröd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Dikeskant vid skogsväg. ( H. europaea enl. Björk 2000 ) Följeväxt mattlummer.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>113158980</v>
       </c>
       <c r="B11" t="n">
-        <v>96320</v>
+        <v>96325</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>113633043</v>
       </c>
       <c r="B12" t="n">
-        <v>96322</v>
+        <v>96325</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>113158980</v>
       </c>
       <c r="B11" t="n">
-        <v>96325</v>
+        <v>96353</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>113633043</v>
       </c>
       <c r="B12" t="n">
-        <v>96325</v>
+        <v>96353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>113158980</v>
       </c>
       <c r="B11" t="n">
-        <v>96353</v>
+        <v>96357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>113633043</v>
       </c>
       <c r="B12" t="n">
-        <v>96353</v>
+        <v>96357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>121221080</v>
       </c>
       <c r="B23" t="n">
-        <v>97018</v>
+        <v>97028</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>121221080</v>
       </c>
       <c r="B23" t="n">
-        <v>97028</v>
+        <v>97041</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>121221080</v>
       </c>
       <c r="B23" t="n">
-        <v>97041</v>
+        <v>97042</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>121221080</v>
       </c>
       <c r="B23" t="n">
-        <v>97042</v>
+        <v>97045</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Niklas Hjort, Erik Ljungstrand, Joakim Ekman, Håkan Andersson</t>
+          <t>Håkan Andersson, Joakim Ekman, Erik Ljungstrand, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>121221080</v>
       </c>
       <c r="B23" t="n">
-        <v>97045</v>
+        <v>97051</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Andersson, Joakim Ekman, Erik Ljungstrand, Niklas Hjort</t>
+          <t>Niklas Hjort, Erik Ljungstrand, Joakim Ekman, Håkan Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -3117,7 +3117,7 @@
         <v>121221080</v>
       </c>
       <c r="B23" t="n">
-        <v>97051</v>
+        <v>97052</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 36315-2020 artfynd.xlsx
+++ b/artfynd/A 36315-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88816161</v>
+        <v>88815935</v>
       </c>
       <c r="B4" t="n">
-        <v>96605</v>
+        <v>95522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6330301</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dråglopplummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia suberecta</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lowe) Tardieu</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,17 +954,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SO om St Bjurevatten, Boh</t>
+          <t>N om Hålt, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323645</v>
+        <v>323294.8536531592</v>
       </c>
       <c r="R4" t="n">
-        <v>6436235</v>
+        <v>6435907.311549278</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,9 +991,19 @@
           <t>2020-10-31</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88815935</v>
+        <v>88816520</v>
       </c>
       <c r="B5" t="n">
-        <v>95522</v>
+        <v>95519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,14 +1071,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N om Hålt, Boh</t>
+          <t>V om L Bjurevatten, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323294.8536531592</v>
+        <v>323722.3691306713</v>
       </c>
       <c r="R5" t="n">
-        <v>6435907.311549278</v>
+        <v>6436239.928961508</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88816031</v>
+        <v>88815907</v>
       </c>
       <c r="B6" t="n">
-        <v>95511</v>
+        <v>95519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,14 +1188,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S om St Bjurevatten, Boh</t>
+          <t>Hålt, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323395.5023633309</v>
+        <v>323246.2701407622</v>
       </c>
       <c r="R6" t="n">
-        <v>6436140.404500294</v>
+        <v>6435578.561780288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88816520</v>
+        <v>113085365</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
+        <v>96508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,38 +1281,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>V om L Bjurevatten, Boh</t>
+          <t>L. Bjurevatten  SV om, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323722.3691306713</v>
+        <v>323785</v>
       </c>
       <c r="R7" t="n">
-        <v>6436239.928961508</v>
+        <v>6436246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,22 +1351,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-31</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På kanten av skogsbäck</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1377,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Stig Ingvarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Stig Ingvarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88815907</v>
+        <v>113158470</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
+        <v>96613</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,16 +1405,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1407,22 +1424,26 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hålt, Boh</t>
+          <t>Skogsvägen 350 m S Stora Bjurevatten, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323246.2701407622</v>
+        <v>323299</v>
       </c>
       <c r="R8" t="n">
-        <v>6435578.561780288</v>
+        <v>6435949</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,22 +1467,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-31</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-31</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I diket O om skogsvägen. Flera skott varav några med skaftade sporax. En meter S om mattlummerbeståndet fanns ett exemplar med två skott av äkta lopplummer (Huperiza europaea).</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1503,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Uno Unger</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Uno Unger, Stig Ingvarsson, Erik Ljungstrand, Eva Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113085365</v>
+        <v>113158980</v>
       </c>
       <c r="B9" t="n">
-        <v>96508</v>
+        <v>96602</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1531,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220686</v>
+        <v>224361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1527,31 +1553,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>L. Bjurevatten  SV om, Boh</t>
+          <t>Skogsvägen 350 m S Stora Bjurevatten, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323785</v>
+        <v>323299</v>
       </c>
       <c r="R9" t="n">
-        <v>6436246</v>
+        <v>6435949</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,17 +1597,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På kanten av skogsbäck</t>
+          <t>I diket O om skogsvägen. Ett exemplar med två skott av den numera urskilda äkta lopplummern (Huperzia europaea) (Björk 2020). En meter N om denna planta fanns ett mattlummerbestånd med några skaftade sporax.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,22 +1633,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Uno Unger</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Uno Unger, Stig Ingvarsson, Erik Ljungstrand, Eva Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113158470</v>
+        <v>113633043</v>
       </c>
       <c r="B10" t="n">
-        <v>96613</v>
+        <v>96602</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,45 +1661,53 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>224361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skogsvägen 350 m S Stora Bjurevatten, Boh</t>
+          <t>Svartsjön, 600 m V om, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323299</v>
+        <v>323298</v>
       </c>
       <c r="R10" t="n">
-        <v>6435949</v>
+        <v>6435947</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,27 +1731,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I diket O om skogsvägen. Flera skott varav några med skaftade sporax. En meter S om mattlummerbeståndet fanns ett exemplar med två skott av äkta lopplummer (Huperiza europaea).</t>
+          <t>Dikeskant vid skogsväg. ( H. europaea enl. Björk 2000 ) Följeväxt mattlummer.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,22 +1757,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Uno Unger</t>
+          <t>Stig Ingvarsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Uno Unger, Stig Ingvarsson, Erik Ljungstrand, Eva Andersson</t>
+          <t>Stig Ingvarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113158980</v>
+        <v>115175132</v>
       </c>
       <c r="B11" t="n">
-        <v>96602</v>
+        <v>102661</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,53 +1781,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224361</v>
+        <v>837</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hypericum pulchrum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skogsvägen 350 m S Stora Bjurevatten, Boh</t>
+          <t>Lilla Bjurevatten, 650 m SV, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323299</v>
+        <v>323301</v>
       </c>
       <c r="R11" t="n">
-        <v>6435949</v>
+        <v>6435957</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,27 +1839,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I diket O om skogsvägen. Ett exemplar med två skott av den numera urskilda äkta lopplummern (Huperzia europaea) (Björk 2020). En meter N om denna planta fanns ett mattlummerbestånd med några skaftade sporax.</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,26 +1853,30 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Markväg</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Uno Unger</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Uno Unger, Stig Ingvarsson, Erik Ljungstrand, Eva Andersson</t>
+          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand, Eva Andersson, Sofia Lund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113633043</v>
+        <v>115175135</v>
       </c>
       <c r="B12" t="n">
         <v>96602</v>
@@ -1902,33 +1909,17 @@
           <t>Björk</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svartsjön, 600 m V om, Boh</t>
+          <t>Lilla Bjurevatten, 650 m SV, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>323298</v>
       </c>
       <c r="R12" t="n">
-        <v>6435947</v>
+        <v>6435942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1955,17 +1946,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Dikeskant vid skogsväg. ( H. europaea enl. Björk 2000 ) Följeväxt mattlummer.</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,29 +1960,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Dikeskant</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stig Ingvarsson</t>
+          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand, Eva Andersson, Sofia Lund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115175132</v>
+        <v>115175134</v>
       </c>
       <c r="B13" t="n">
-        <v>102661</v>
+        <v>96614</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2005,27 +1995,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>837</v>
+        <v>224364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypericum pulchrum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2033,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323301</v>
+        <v>323298</v>
       </c>
       <c r="R13" t="n">
-        <v>6435957</v>
+        <v>6435942</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2068,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Markväg</t>
+          <t>Dikeskant</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2100,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115175135</v>
+        <v>116146633</v>
       </c>
       <c r="B14" t="n">
-        <v>96602</v>
+        <v>96693</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2116,37 +2102,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilla Bjurevatten, 650 m SV, Boh</t>
+          <t>S om bäcken mellan Lilla och Stora Bjurevatten, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323298</v>
+        <v>323677</v>
       </c>
       <c r="R14" t="n">
-        <v>6435942</v>
+        <v>6436218</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,12 +2164,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett mindre bestånd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,33 +2193,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Dikeskant</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Uno Unger</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand, Eva Andersson, Sofia Lund</t>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Stig Ingvarsson, Mathias Theander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115175134</v>
+        <v>116146576</v>
       </c>
       <c r="B15" t="n">
-        <v>96614</v>
+        <v>96685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,33 +2228,53 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224364</v>
+        <v>224361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Bjurevatten, 650 m SV, Boh</t>
+          <t>S om bäcken mellan Lilla och Stora Bjurevatten, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323298</v>
+        <v>323677</v>
       </c>
       <c r="R15" t="n">
-        <v>6435942</v>
+        <v>6436218</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2273,12 +2298,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Upptäcktes av Sofia Mattiasson Nilsson.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,33 +2327,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Dikeskant</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Uno Unger</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand, Eva Andersson, Sofia Lund</t>
+          <t>Eva Andersson, Erik Ljungstrand, Uno Unger, Stig Ingvarsson, Sofia Mattiasson Nilsson, Lars Erik Norbäck, Mathias Theander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116116599</v>
+        <v>119360813</v>
       </c>
       <c r="B16" t="n">
-        <v>96686</v>
+        <v>102929</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,46 +2358,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6052779</v>
+        <v>837</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hypericum pulchrum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartedalen, Boh</t>
+          <t>Svartedalen, Svedjan NO, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>323691</v>
+        <v>323218</v>
       </c>
       <c r="R16" t="n">
-        <v>6436217</v>
+        <v>6435560</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2388,17 +2416,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>BFiG exkursion</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,29 +2430,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulf Persson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116146633</v>
+        <v>119360814</v>
       </c>
       <c r="B17" t="n">
-        <v>96693</v>
+        <v>102929</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,20 +2465,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>837</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypericum pulchrum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2460,27 +2487,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>S om bäcken mellan Lilla och Stora Bjurevatten, Boh</t>
+          <t>Svartedalen, Svedjan NO, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>323677</v>
+        <v>323227</v>
       </c>
       <c r="R17" t="n">
-        <v>6436218</v>
+        <v>6435592</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2504,27 +2523,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett mindre bestånd.</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2533,29 +2537,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Uno Unger</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Stig Ingvarsson, Mathias Theander</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116146599</v>
+        <v>119360816</v>
       </c>
       <c r="B18" t="n">
-        <v>96686</v>
+        <v>102929</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,57 +2572,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6052779</v>
+        <v>837</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön groddlummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hypericum pulchrum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>S om bäcken mellan Lilla och Stora Bjurevatten, Boh</t>
+          <t>Svartedalen, Svedjan NO, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>323677</v>
+        <v>323306</v>
       </c>
       <c r="R18" t="n">
-        <v>6436218</v>
+        <v>6435963</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2638,27 +2630,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Upptäcktes av Sofia Mattiasson Nilsson.</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,572 +2644,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Uno Unger</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Stig Ingvarsson, Sofia Mattiasson Nilsson, Mathias Theander</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>116660462</v>
-      </c>
-      <c r="B19" t="n">
-        <v>96723</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6052779</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Grön groddlummer</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Svartedalen, Stora Bjurevatten syd, Boh</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>323683</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6436220</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Stenungsund</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Spekeröd</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>119360813</v>
-      </c>
-      <c r="B20" t="n">
-        <v>102929</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>837</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Hedjohannesört</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hypericum pulchrum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Svartedalen, Svedjan NO, Boh</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>323218</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6435560</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Stenungsund</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Spekeröd</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Skogsväg</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>119360814</v>
-      </c>
-      <c r="B21" t="n">
-        <v>102929</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>837</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Hedjohannesört</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hypericum pulchrum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Svartedalen, Svedjan NO, Boh</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>323227</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6435592</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Stenungsund</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Spekeröd</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Skogsväg</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>119360816</v>
-      </c>
-      <c r="B22" t="n">
-        <v>102929</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>837</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Hedjohannesört</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Hypericum pulchrum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Svartedalen, Svedjan NO, Boh</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>323306</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6435963</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Stenungsund</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Spekeröd</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2024-07-21</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Skogsväg</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>121221080</v>
-      </c>
-      <c r="B23" t="n">
-        <v>97052</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6052779</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Grön groddlummer</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) Schrank &amp; Mart. sensu stricto</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Lilla Bjurevatten, Boh</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>323683</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6436222</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Stenungsund</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Spekeröd</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Känd förekomst förevisad av Erik Ljungstrand.</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Niklas Hjort</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Niklas Hjort, Erik Ljungstrand, Joakim Ekman, Håkan Andersson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
